--- a/Scout/crk-vs-crp-090426.xlsx
+++ b/Scout/crk-vs-crp-090426.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rba6d8dcb2e90424d"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R09b6c1697b50412d"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -133,6 +148,9 @@
     <t>Rush</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>DEUCE</t>
   </si>
   <si>
@@ -163,6 +181,9 @@
     <t>B</t>
   </si>
   <si>
+    <t>G DOT</t>
+  </si>
+  <si>
     <t>PRO</t>
   </si>
   <si>
@@ -178,6 +199,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>K DOT</t>
+  </si>
+  <si>
     <t>TWINS OVER</t>
   </si>
   <si>
@@ -193,6 +217,9 @@
     <t>A</t>
   </si>
   <si>
+    <t>GUN STACK G</t>
+  </si>
+  <si>
     <t>QB FOLLOW</t>
   </si>
   <si>
@@ -232,6 +259,9 @@
     <t>Sack</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>HB SCREEN</t>
   </si>
   <si>
@@ -295,6 +325,12 @@
     <t>WING TRIPS</t>
   </si>
   <si>
+    <t>K GUN</t>
+  </si>
+  <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>Y TRIPS CLOSED</t>
   </si>
   <si>
@@ -304,10 +340,16 @@
     <t>E-Alley</t>
   </si>
   <si>
+    <t>GUN STACK K</t>
+  </si>
+  <si>
     <t>QB SWEEP</t>
   </si>
   <si>
     <t>ZONE READ</t>
+  </si>
+  <si>
+    <t>G DOT UNDER</t>
   </si>
   <si>
     <t>QB SNEAK</t>
@@ -329,7 +371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y140"/>
+  <dimension ref="A1:AC140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -407,6 +449,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -416,7 +470,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -427,7 +481,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -438,7 +492,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -449,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -460,7 +514,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -471,19 +525,19 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>-40</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -494,7 +548,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -506,30 +560,33 @@
         <v>-35</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J8">
         <v>9</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s">
-        <v>35</v>
-      </c>
-      <c r="S8" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8" t="s">
-        <v>37</v>
-      </c>
-      <c r="X8">
+        <v>38</v>
+      </c>
+      <c r="P8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W8" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -541,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -553,30 +610,33 @@
         <v>-44</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
         <v>38</v>
       </c>
-      <c r="I9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="P9" t="s">
+        <v>45</v>
+      </c>
+      <c r="W9" t="s">
         <v>40</v>
       </c>
-      <c r="U9" t="s">
-        <v>37</v>
-      </c>
-      <c r="X9">
+      <c r="X9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -588,7 +648,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -600,24 +660,27 @@
         <v>-45</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U10" t="s">
-        <v>31</v>
-      </c>
-      <c r="X10">
+        <v>47</v>
+      </c>
+      <c r="P10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -629,7 +692,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -641,33 +704,36 @@
         <v>-46</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" t="s">
         <v>39</v>
       </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-      <c r="R11" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" t="s">
-        <v>42</v>
-      </c>
-      <c r="U11" t="s">
-        <v>37</v>
-      </c>
-      <c r="V11" t="s">
-        <v>31</v>
-      </c>
-      <c r="X11">
+      <c r="W11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -679,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -691,30 +757,33 @@
         <v>-48</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>41</v>
-      </c>
-      <c r="R12" t="s">
-        <v>31</v>
-      </c>
-      <c r="S12" t="s">
-        <v>44</v>
-      </c>
-      <c r="U12" t="s">
-        <v>37</v>
-      </c>
-      <c r="X12">
+        <v>47</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+      <c r="W12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -726,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -738,18 +807,18 @@
         <v>-48</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J13">
         <v>-5</v>
       </c>
-      <c r="X13">
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -761,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -773,15 +842,15 @@
         <v>-43</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
-      </c>
-      <c r="X14">
+        <v>53</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -793,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -805,39 +874,42 @@
         <v>-30</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
         <v>38</v>
       </c>
-      <c r="I15" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15" t="s">
-        <v>34</v>
-      </c>
       <c r="L15">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>49</v>
-      </c>
-      <c r="R15" t="s">
-        <v>31</v>
-      </c>
-      <c r="S15" t="s">
-        <v>50</v>
-      </c>
-      <c r="T15" t="s">
-        <v>51</v>
-      </c>
-      <c r="U15" t="s">
-        <v>31</v>
-      </c>
-      <c r="X15">
+        <v>55</v>
+      </c>
+      <c r="P15" t="s">
+        <v>56</v>
+      </c>
+      <c r="W15" t="s">
+        <v>35</v>
+      </c>
+      <c r="X15" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -849,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -861,19 +933,19 @@
         <v>-33</v>
       </c>
       <c r="G16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" t="s">
         <v>37</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>33</v>
       </c>
       <c r="J16">
         <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -884,19 +956,22 @@
       <c r="O16">
         <v>9</v>
       </c>
-      <c r="R16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S16" t="s">
-        <v>52</v>
-      </c>
-      <c r="T16" t="s">
-        <v>53</v>
-      </c>
-      <c r="U16" t="s">
-        <v>37</v>
-      </c>
-      <c r="X16">
+      <c r="P16" t="s">
+        <v>56</v>
+      </c>
+      <c r="W16" t="s">
+        <v>42</v>
+      </c>
+      <c r="X16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -908,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -920,39 +995,42 @@
         <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J17">
         <v>7</v>
       </c>
       <c r="K17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
-      </c>
-      <c r="R17" t="s">
-        <v>31</v>
-      </c>
-      <c r="S17" t="s">
-        <v>55</v>
-      </c>
-      <c r="T17" t="s">
-        <v>56</v>
-      </c>
-      <c r="U17" t="s">
-        <v>31</v>
-      </c>
-      <c r="X17">
+        <v>61</v>
+      </c>
+      <c r="P17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W17" t="s">
+        <v>35</v>
+      </c>
+      <c r="X17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -964,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -976,19 +1054,19 @@
         <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18">
         <v>3</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -999,19 +1077,22 @@
       <c r="O18">
         <v>3</v>
       </c>
-      <c r="R18" t="s">
-        <v>37</v>
-      </c>
-      <c r="S18" t="s">
-        <v>57</v>
-      </c>
-      <c r="T18" t="s">
-        <v>58</v>
-      </c>
-      <c r="U18" t="s">
-        <v>37</v>
-      </c>
-      <c r="X18">
+      <c r="P18" t="s">
+        <v>45</v>
+      </c>
+      <c r="W18" t="s">
+        <v>42</v>
+      </c>
+      <c r="X18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1023,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1035,39 +1116,42 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19" t="s">
         <v>38</v>
-      </c>
-      <c r="I19" t="s">
-        <v>39</v>
-      </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
-      <c r="K19" t="s">
-        <v>34</v>
       </c>
       <c r="L19">
         <v>8</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
-      </c>
-      <c r="R19" t="s">
-        <v>31</v>
-      </c>
-      <c r="S19" t="s">
-        <v>55</v>
-      </c>
-      <c r="T19" t="s">
-        <v>60</v>
-      </c>
-      <c r="U19" t="s">
-        <v>31</v>
-      </c>
-      <c r="X19">
+        <v>67</v>
+      </c>
+      <c r="P19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W19" t="s">
+        <v>35</v>
+      </c>
+      <c r="X19" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1079,7 +1163,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -1091,19 +1175,19 @@
         <v>24</v>
       </c>
       <c r="G20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" t="s">
         <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" t="s">
-        <v>33</v>
       </c>
       <c r="J20">
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -1114,19 +1198,22 @@
       <c r="O20">
         <v>1</v>
       </c>
-      <c r="R20" t="s">
-        <v>31</v>
-      </c>
-      <c r="S20" t="s">
-        <v>55</v>
-      </c>
-      <c r="T20" t="s">
-        <v>53</v>
-      </c>
-      <c r="U20" t="s">
-        <v>31</v>
-      </c>
-      <c r="X20">
+      <c r="P20" t="s">
+        <v>56</v>
+      </c>
+      <c r="W20" t="s">
+        <v>35</v>
+      </c>
+      <c r="X20" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB20">
         <v>1</v>
       </c>
     </row>
@@ -1138,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -1150,39 +1237,42 @@
         <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J21">
         <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
       <c r="M21" t="s">
-        <v>54</v>
-      </c>
-      <c r="R21" t="s">
-        <v>37</v>
-      </c>
-      <c r="S21" t="s">
-        <v>55</v>
-      </c>
-      <c r="T21" t="s">
-        <v>60</v>
-      </c>
-      <c r="U21" t="s">
-        <v>37</v>
-      </c>
-      <c r="X21">
+        <v>61</v>
+      </c>
+      <c r="P21" t="s">
+        <v>56</v>
+      </c>
+      <c r="W21" t="s">
+        <v>42</v>
+      </c>
+      <c r="X21" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB21">
         <v>1</v>
       </c>
     </row>
@@ -1194,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1206,36 +1296,39 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J22">
         <v>7</v>
       </c>
       <c r="K22" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L22">
         <v>6</v>
       </c>
-      <c r="R22" t="s">
-        <v>31</v>
-      </c>
-      <c r="S22" t="s">
-        <v>42</v>
-      </c>
-      <c r="T22" t="s">
-        <v>62</v>
-      </c>
-      <c r="U22" t="s">
-        <v>31</v>
-      </c>
-      <c r="X22">
+      <c r="P22" t="s">
+        <v>45</v>
+      </c>
+      <c r="W22" t="s">
+        <v>35</v>
+      </c>
+      <c r="X22" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB22">
         <v>1</v>
       </c>
     </row>
@@ -1247,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1259,39 +1352,42 @@
         <v>7</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L23">
         <v>7</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
-      </c>
-      <c r="R23" t="s">
-        <v>31</v>
-      </c>
-      <c r="S23" t="s">
-        <v>55</v>
-      </c>
-      <c r="T23" t="s">
-        <v>56</v>
-      </c>
-      <c r="U23" t="s">
-        <v>31</v>
-      </c>
-      <c r="X23">
+        <v>61</v>
+      </c>
+      <c r="P23" t="s">
+        <v>62</v>
+      </c>
+      <c r="W23" t="s">
+        <v>35</v>
+      </c>
+      <c r="X23" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB23">
         <v>1</v>
       </c>
     </row>
@@ -1303,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1315,39 +1411,42 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L24">
         <v>8</v>
       </c>
       <c r="M24" t="s">
-        <v>49</v>
-      </c>
-      <c r="R24" t="s">
-        <v>37</v>
-      </c>
-      <c r="S24" t="s">
         <v>55</v>
       </c>
-      <c r="T24" t="s">
-        <v>60</v>
-      </c>
-      <c r="U24" t="s">
-        <v>37</v>
-      </c>
-      <c r="X24">
+      <c r="P24" t="s">
+        <v>68</v>
+      </c>
+      <c r="W24" t="s">
+        <v>42</v>
+      </c>
+      <c r="X24" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB24">
         <v>1</v>
       </c>
     </row>
@@ -1359,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1368,15 +1467,15 @@
         <v>3</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>65</v>
-      </c>
-      <c r="X25">
+        <v>74</v>
+      </c>
+      <c r="AB25">
         <v>1</v>
       </c>
     </row>
@@ -1388,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1397,15 +1496,15 @@
         <v>-40</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>47</v>
-      </c>
-      <c r="X26">
+        <v>53</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1417,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1429,30 +1528,33 @@
         <v>-22</v>
       </c>
       <c r="G27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>41</v>
-      </c>
-      <c r="R27" t="s">
-        <v>31</v>
-      </c>
-      <c r="S27" t="s">
-        <v>44</v>
-      </c>
-      <c r="U27" t="s">
-        <v>37</v>
-      </c>
-      <c r="X27">
+        <v>47</v>
+      </c>
+      <c r="P27" t="s">
+        <v>45</v>
+      </c>
+      <c r="W27" t="s">
+        <v>35</v>
+      </c>
+      <c r="X27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1464,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1476,30 +1578,33 @@
         <v>-22</v>
       </c>
       <c r="G28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
+        <v>47</v>
+      </c>
+      <c r="P28" t="s">
         <v>39</v>
       </c>
-      <c r="J28">
-        <v>4</v>
-      </c>
-      <c r="K28" t="s">
-        <v>41</v>
-      </c>
-      <c r="R28" t="s">
-        <v>35</v>
-      </c>
-      <c r="S28" t="s">
-        <v>42</v>
-      </c>
-      <c r="U28" t="s">
-        <v>37</v>
-      </c>
-      <c r="X28">
+      <c r="W28" t="s">
+        <v>40</v>
+      </c>
+      <c r="X28" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1511,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1523,30 +1628,33 @@
         <v>-26</v>
       </c>
       <c r="G29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" t="s">
         <v>37</v>
-      </c>
-      <c r="H29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" t="s">
-        <v>33</v>
       </c>
       <c r="J29">
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>34</v>
-      </c>
-      <c r="R29" t="s">
-        <v>35</v>
-      </c>
-      <c r="S29" t="s">
-        <v>36</v>
-      </c>
-      <c r="U29" t="s">
-        <v>31</v>
-      </c>
-      <c r="X29">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>45</v>
+      </c>
+      <c r="W29" t="s">
+        <v>40</v>
+      </c>
+      <c r="X29" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1558,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1570,24 +1678,27 @@
         <v>-41</v>
       </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J30">
         <v>-10</v>
       </c>
       <c r="K30" t="s">
-        <v>41</v>
-      </c>
-      <c r="U30" t="s">
-        <v>37</v>
-      </c>
-      <c r="X30">
+        <v>47</v>
+      </c>
+      <c r="P30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1599,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1611,30 +1722,33 @@
         <v>-31</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I31" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J31">
         <v>29</v>
       </c>
       <c r="K31" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" t="s">
-        <v>31</v>
-      </c>
-      <c r="S31" t="s">
-        <v>57</v>
-      </c>
-      <c r="U31" t="s">
-        <v>31</v>
-      </c>
-      <c r="X31">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>30</v>
+      </c>
+      <c r="W31" t="s">
+        <v>35</v>
+      </c>
+      <c r="X31" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1646,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1658,30 +1772,33 @@
         <v>40</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I32" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J32">
         <v>12</v>
       </c>
       <c r="K32" t="s">
-        <v>34</v>
-      </c>
-      <c r="R32" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" t="s">
-        <v>42</v>
-      </c>
-      <c r="U32" t="s">
-        <v>31</v>
-      </c>
-      <c r="X32">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>39</v>
+      </c>
+      <c r="W32" t="s">
+        <v>40</v>
+      </c>
+      <c r="X32" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
     </row>
@@ -1693,7 +1810,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1705,24 +1822,27 @@
         <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J33">
         <v>5</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
-      </c>
-      <c r="R33" t="s">
-        <v>31</v>
-      </c>
-      <c r="S33" t="s">
-        <v>57</v>
-      </c>
-      <c r="X33">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>30</v>
+      </c>
+      <c r="W33" t="s">
+        <v>35</v>
+      </c>
+      <c r="X33" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB33">
         <v>2</v>
       </c>
     </row>
@@ -1734,7 +1854,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1746,30 +1866,33 @@
         <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H34" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34">
+        <v>7</v>
+      </c>
+      <c r="K34" t="s">
         <v>38</v>
       </c>
-      <c r="I34" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34">
-        <v>7</v>
-      </c>
-      <c r="K34" t="s">
-        <v>34</v>
-      </c>
-      <c r="R34" t="s">
-        <v>31</v>
-      </c>
-      <c r="S34" t="s">
-        <v>57</v>
-      </c>
-      <c r="U34" t="s">
-        <v>31</v>
-      </c>
-      <c r="X34">
+      <c r="P34" t="s">
+        <v>30</v>
+      </c>
+      <c r="W34" t="s">
+        <v>35</v>
+      </c>
+      <c r="X34" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB34">
         <v>2</v>
       </c>
     </row>
@@ -1781,7 +1904,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1793,30 +1916,33 @@
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J35">
         <v>16</v>
       </c>
       <c r="K35" t="s">
-        <v>34</v>
-      </c>
-      <c r="R35" t="s">
-        <v>37</v>
-      </c>
-      <c r="S35" t="s">
-        <v>57</v>
-      </c>
-      <c r="U35" t="s">
-        <v>37</v>
-      </c>
-      <c r="X35">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>45</v>
+      </c>
+      <c r="W35" t="s">
+        <v>42</v>
+      </c>
+      <c r="X35" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB35">
         <v>2</v>
       </c>
     </row>
@@ -1828,7 +1954,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1837,15 +1963,15 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H36" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
-      </c>
-      <c r="X36">
+        <v>77</v>
+      </c>
+      <c r="AB36">
         <v>2</v>
       </c>
     </row>
@@ -1857,19 +1983,19 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F37">
         <v>-40</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -1880,7 +2006,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1892,39 +2018,42 @@
         <v>-20</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I38" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L38">
         <v>7</v>
       </c>
       <c r="M38" t="s">
-        <v>49</v>
-      </c>
-      <c r="R38" t="s">
-        <v>31</v>
-      </c>
-      <c r="S38" t="s">
-        <v>44</v>
-      </c>
-      <c r="T38" t="s">
-        <v>71</v>
-      </c>
-      <c r="U38" t="s">
-        <v>31</v>
-      </c>
-      <c r="X38">
+        <v>55</v>
+      </c>
+      <c r="P38" t="s">
+        <v>45</v>
+      </c>
+      <c r="W38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X38" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB38">
         <v>2</v>
       </c>
     </row>
@@ -1936,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -1948,36 +2077,39 @@
         <v>-20</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J39">
         <v>-13</v>
       </c>
       <c r="K39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L39">
         <v>6</v>
       </c>
-      <c r="R39" t="s">
-        <v>37</v>
-      </c>
-      <c r="S39" t="s">
-        <v>42</v>
-      </c>
-      <c r="T39" t="s">
-        <v>62</v>
-      </c>
-      <c r="U39" t="s">
-        <v>37</v>
-      </c>
-      <c r="X39">
+      <c r="P39" t="s">
+        <v>45</v>
+      </c>
+      <c r="W39" t="s">
+        <v>42</v>
+      </c>
+      <c r="X39" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB39">
         <v>2</v>
       </c>
     </row>
@@ -1989,7 +2121,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2001,19 +2133,19 @@
         <v>-7</v>
       </c>
       <c r="G40" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" t="s">
         <v>37</v>
-      </c>
-      <c r="H40" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" t="s">
-        <v>33</v>
       </c>
       <c r="J40">
         <v>-3</v>
       </c>
       <c r="K40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -2024,19 +2156,22 @@
       <c r="O40">
         <v>3</v>
       </c>
-      <c r="R40" t="s">
-        <v>37</v>
-      </c>
-      <c r="S40" t="s">
-        <v>57</v>
-      </c>
-      <c r="T40" t="s">
-        <v>73</v>
-      </c>
-      <c r="U40" t="s">
-        <v>37</v>
-      </c>
-      <c r="X40">
+      <c r="P40" t="s">
+        <v>82</v>
+      </c>
+      <c r="W40" t="s">
+        <v>42</v>
+      </c>
+      <c r="X40" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB40">
         <v>2</v>
       </c>
     </row>
@@ -2048,7 +2183,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2060,15 +2195,15 @@
         <v>-4</v>
       </c>
       <c r="G41" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H41" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s">
-        <v>47</v>
-      </c>
-      <c r="X41">
+        <v>53</v>
+      </c>
+      <c r="AB41">
         <v>2</v>
       </c>
     </row>
@@ -2080,7 +2215,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2092,30 +2227,33 @@
         <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H42" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I42" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J42">
         <v>-3</v>
       </c>
       <c r="K42" t="s">
-        <v>41</v>
-      </c>
-      <c r="R42" t="s">
-        <v>31</v>
-      </c>
-      <c r="S42" t="s">
-        <v>57</v>
-      </c>
-      <c r="U42" t="s">
-        <v>37</v>
-      </c>
-      <c r="X42">
+        <v>47</v>
+      </c>
+      <c r="P42" t="s">
+        <v>82</v>
+      </c>
+      <c r="W42" t="s">
+        <v>35</v>
+      </c>
+      <c r="X42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2127,7 +2265,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2139,30 +2277,33 @@
         <v>33</v>
       </c>
       <c r="G43" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H43" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>41</v>
-      </c>
-      <c r="R43" t="s">
-        <v>31</v>
-      </c>
-      <c r="S43" t="s">
-        <v>44</v>
-      </c>
-      <c r="U43" t="s">
-        <v>37</v>
-      </c>
-      <c r="X43">
+        <v>47</v>
+      </c>
+      <c r="P43" t="s">
+        <v>82</v>
+      </c>
+      <c r="W43" t="s">
+        <v>35</v>
+      </c>
+      <c r="X43" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2174,7 +2315,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -2186,30 +2327,33 @@
         <v>33</v>
       </c>
       <c r="G44" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H44" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J44">
         <v>-9</v>
       </c>
       <c r="K44" t="s">
-        <v>41</v>
-      </c>
-      <c r="R44" t="s">
-        <v>31</v>
-      </c>
-      <c r="S44" t="s">
-        <v>75</v>
-      </c>
-      <c r="U44" t="s">
-        <v>37</v>
-      </c>
-      <c r="X44">
+        <v>47</v>
+      </c>
+      <c r="P44" t="s">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s">
+        <v>35</v>
+      </c>
+      <c r="X44" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2221,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2233,15 +2377,15 @@
         <v>42</v>
       </c>
       <c r="G45" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I45" t="s">
-        <v>76</v>
-      </c>
-      <c r="X45">
+        <v>86</v>
+      </c>
+      <c r="AB45">
         <v>3</v>
       </c>
     </row>
@@ -2253,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2265,39 +2409,42 @@
         <v>-14</v>
       </c>
       <c r="G46" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" t="s">
+        <v>44</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46" t="s">
         <v>38</v>
-      </c>
-      <c r="I46" t="s">
-        <v>39</v>
-      </c>
-      <c r="J46">
-        <v>2</v>
-      </c>
-      <c r="K46" t="s">
-        <v>34</v>
       </c>
       <c r="L46">
         <v>8</v>
       </c>
       <c r="M46" t="s">
-        <v>30</v>
-      </c>
-      <c r="R46" t="s">
-        <v>31</v>
-      </c>
-      <c r="S46" t="s">
-        <v>55</v>
-      </c>
-      <c r="T46" t="s">
-        <v>77</v>
-      </c>
-      <c r="U46" t="s">
-        <v>31</v>
-      </c>
-      <c r="X46">
+        <v>34</v>
+      </c>
+      <c r="P46" t="s">
+        <v>56</v>
+      </c>
+      <c r="W46" t="s">
+        <v>35</v>
+      </c>
+      <c r="X46" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -2309,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2321,19 +2468,19 @@
         <v>-16</v>
       </c>
       <c r="G47" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J47">
         <v>-8</v>
       </c>
       <c r="K47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L47">
         <v>8</v>
@@ -2344,19 +2491,22 @@
       <c r="O47">
         <v>1</v>
       </c>
-      <c r="R47" t="s">
-        <v>31</v>
-      </c>
-      <c r="S47" t="s">
-        <v>55</v>
-      </c>
-      <c r="T47" t="s">
-        <v>62</v>
-      </c>
-      <c r="U47" t="s">
-        <v>31</v>
-      </c>
-      <c r="X47">
+      <c r="P47" t="s">
+        <v>56</v>
+      </c>
+      <c r="W47" t="s">
+        <v>35</v>
+      </c>
+      <c r="X47" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2368,7 +2518,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2380,18 +2530,18 @@
         <v>-8</v>
       </c>
       <c r="G48" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I48" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>34</v>
-      </c>
-      <c r="X48">
+        <v>38</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -2403,7 +2553,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2415,39 +2565,42 @@
         <v>-8</v>
       </c>
       <c r="G49" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I49" t="s">
+        <v>44</v>
+      </c>
+      <c r="J49">
+        <v>3</v>
+      </c>
+      <c r="K49" t="s">
         <v>38</v>
       </c>
-      <c r="I49" t="s">
-        <v>39</v>
-      </c>
-      <c r="J49">
-        <v>3</v>
-      </c>
-      <c r="K49" t="s">
-        <v>34</v>
-      </c>
       <c r="L49">
         <v>7</v>
       </c>
       <c r="M49" t="s">
-        <v>59</v>
-      </c>
-      <c r="R49" t="s">
-        <v>37</v>
-      </c>
-      <c r="S49" t="s">
-        <v>50</v>
-      </c>
-      <c r="T49" t="s">
-        <v>79</v>
-      </c>
-      <c r="U49" t="s">
-        <v>37</v>
-      </c>
-      <c r="X49">
+        <v>67</v>
+      </c>
+      <c r="P49" t="s">
+        <v>62</v>
+      </c>
+      <c r="W49" t="s">
+        <v>42</v>
+      </c>
+      <c r="X49" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2459,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2471,19 +2624,19 @@
         <v>-11</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I50" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L50">
         <v>6</v>
@@ -2494,19 +2647,22 @@
       <c r="O50">
         <v>6</v>
       </c>
-      <c r="R50" t="s">
-        <v>31</v>
-      </c>
-      <c r="S50" t="s">
-        <v>57</v>
-      </c>
-      <c r="T50" t="s">
-        <v>80</v>
-      </c>
-      <c r="U50" t="s">
-        <v>37</v>
-      </c>
-      <c r="X50">
+      <c r="P50" t="s">
+        <v>45</v>
+      </c>
+      <c r="W50" t="s">
+        <v>35</v>
+      </c>
+      <c r="X50" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2518,7 +2674,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2530,18 +2686,18 @@
         <v>-11</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
-      <c r="X51">
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2553,7 +2709,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2565,15 +2721,15 @@
         <v>3</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>65</v>
-      </c>
-      <c r="X52">
+        <v>74</v>
+      </c>
+      <c r="AB52">
         <v>4</v>
       </c>
     </row>
@@ -2585,7 +2741,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2594,15 +2750,15 @@
         <v>-40</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I53" t="s">
-        <v>70</v>
-      </c>
-      <c r="X53">
+        <v>79</v>
+      </c>
+      <c r="AB53">
         <v>5</v>
       </c>
     </row>
@@ -2614,7 +2770,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2626,42 +2782,45 @@
         <v>-20</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I54" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L54">
         <v>7</v>
       </c>
       <c r="M54" t="s">
-        <v>54</v>
-      </c>
-      <c r="R54" t="s">
-        <v>37</v>
-      </c>
-      <c r="S54" t="s">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s">
-        <v>83</v>
-      </c>
-      <c r="U54" t="s">
-        <v>31</v>
-      </c>
-      <c r="V54" t="s">
-        <v>31</v>
-      </c>
-      <c r="X54">
+        <v>61</v>
+      </c>
+      <c r="P54" t="s">
+        <v>45</v>
+      </c>
+      <c r="W54" t="s">
+        <v>42</v>
+      </c>
+      <c r="X54" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -2673,7 +2832,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2685,19 +2844,19 @@
         <v>-20</v>
       </c>
       <c r="G55" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H55" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L55">
         <v>6</v>
@@ -2708,19 +2867,22 @@
       <c r="O55">
         <v>3</v>
       </c>
-      <c r="R55" t="s">
-        <v>37</v>
-      </c>
-      <c r="S55" t="s">
-        <v>57</v>
-      </c>
-      <c r="T55" t="s">
-        <v>84</v>
-      </c>
-      <c r="U55" t="s">
-        <v>37</v>
-      </c>
-      <c r="X55">
+      <c r="P55" t="s">
+        <v>45</v>
+      </c>
+      <c r="W55" t="s">
+        <v>42</v>
+      </c>
+      <c r="X55" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -2732,7 +2894,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -2744,19 +2906,19 @@
         <v>-20</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I56" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J56">
         <v>11</v>
       </c>
       <c r="K56" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -2767,19 +2929,22 @@
       <c r="O56">
         <v>4</v>
       </c>
-      <c r="R56" t="s">
-        <v>37</v>
-      </c>
-      <c r="S56" t="s">
-        <v>57</v>
-      </c>
-      <c r="T56" t="s">
-        <v>80</v>
-      </c>
-      <c r="U56" t="s">
-        <v>31</v>
-      </c>
-      <c r="X56">
+      <c r="P56" t="s">
+        <v>45</v>
+      </c>
+      <c r="W56" t="s">
+        <v>42</v>
+      </c>
+      <c r="X56" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB56">
         <v>4</v>
       </c>
     </row>
@@ -2791,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2803,39 +2968,42 @@
         <v>-31</v>
       </c>
       <c r="G57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H57" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
         <v>38</v>
       </c>
-      <c r="I57" t="s">
-        <v>39</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="K57" t="s">
-        <v>34</v>
-      </c>
       <c r="L57">
         <v>7</v>
       </c>
       <c r="M57" t="s">
-        <v>59</v>
-      </c>
-      <c r="R57" t="s">
-        <v>37</v>
-      </c>
-      <c r="S57" t="s">
-        <v>85</v>
-      </c>
-      <c r="T57" t="s">
-        <v>86</v>
-      </c>
-      <c r="U57" t="s">
-        <v>31</v>
-      </c>
-      <c r="X57">
+        <v>67</v>
+      </c>
+      <c r="P57" t="s">
+        <v>45</v>
+      </c>
+      <c r="W57" t="s">
+        <v>42</v>
+      </c>
+      <c r="X57" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
     </row>
@@ -2847,7 +3015,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2859,39 +3027,42 @@
         <v>-32</v>
       </c>
       <c r="G58" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H58" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I58" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L58">
         <v>7</v>
       </c>
       <c r="M58" t="s">
-        <v>59</v>
-      </c>
-      <c r="R58" t="s">
-        <v>37</v>
-      </c>
-      <c r="S58" t="s">
-        <v>50</v>
-      </c>
-      <c r="T58" t="s">
-        <v>51</v>
-      </c>
-      <c r="U58" t="s">
-        <v>31</v>
-      </c>
-      <c r="X58">
+        <v>67</v>
+      </c>
+      <c r="P58" t="s">
+        <v>62</v>
+      </c>
+      <c r="W58" t="s">
+        <v>42</v>
+      </c>
+      <c r="X58" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
     </row>
@@ -2903,7 +3074,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2915,19 +3086,19 @@
         <v>-32</v>
       </c>
       <c r="G59" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H59" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L59">
         <v>6</v>
@@ -2938,19 +3109,22 @@
       <c r="O59">
         <v>3</v>
       </c>
-      <c r="R59" t="s">
-        <v>37</v>
-      </c>
-      <c r="S59" t="s">
-        <v>57</v>
-      </c>
-      <c r="T59" t="s">
-        <v>80</v>
-      </c>
-      <c r="U59" t="s">
-        <v>37</v>
-      </c>
-      <c r="X59">
+      <c r="P59" t="s">
+        <v>45</v>
+      </c>
+      <c r="W59" t="s">
+        <v>42</v>
+      </c>
+      <c r="X59" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -2962,7 +3136,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -2974,15 +3148,15 @@
         <v>-32</v>
       </c>
       <c r="G60" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H60" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I60" t="s">
-        <v>47</v>
-      </c>
-      <c r="X60">
+        <v>53</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -2994,7 +3168,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3006,30 +3180,33 @@
         <v>-44</v>
       </c>
       <c r="G61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H61" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I61" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J61">
         <v>-1</v>
       </c>
       <c r="K61" t="s">
-        <v>41</v>
-      </c>
-      <c r="R61" t="s">
-        <v>37</v>
-      </c>
-      <c r="S61" t="s">
-        <v>87</v>
-      </c>
-      <c r="U61" t="s">
-        <v>37</v>
-      </c>
-      <c r="X61">
+        <v>47</v>
+      </c>
+      <c r="P61" t="s">
+        <v>45</v>
+      </c>
+      <c r="W61" t="s">
+        <v>42</v>
+      </c>
+      <c r="X61" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB61">
         <v>5</v>
       </c>
     </row>
@@ -3041,7 +3218,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3053,30 +3230,33 @@
         <v>-43</v>
       </c>
       <c r="G62" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I62" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>41</v>
-      </c>
-      <c r="R62" t="s">
-        <v>31</v>
-      </c>
-      <c r="S62" t="s">
-        <v>57</v>
-      </c>
-      <c r="U62" t="s">
-        <v>37</v>
-      </c>
-      <c r="X62">
+        <v>47</v>
+      </c>
+      <c r="P62" t="s">
+        <v>30</v>
+      </c>
+      <c r="W62" t="s">
+        <v>35</v>
+      </c>
+      <c r="X62" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB62">
         <v>5</v>
       </c>
     </row>
@@ -3088,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -3100,30 +3280,33 @@
         <v>-44</v>
       </c>
       <c r="G63" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H63" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>41</v>
-      </c>
-      <c r="R63" t="s">
-        <v>31</v>
-      </c>
-      <c r="S63" t="s">
-        <v>57</v>
-      </c>
-      <c r="U63" t="s">
-        <v>37</v>
-      </c>
-      <c r="X63">
+        <v>47</v>
+      </c>
+      <c r="P63" t="s">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s">
+        <v>35</v>
+      </c>
+      <c r="X63" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB63">
         <v>5</v>
       </c>
     </row>
@@ -3135,7 +3318,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <v>4</v>
@@ -3147,15 +3330,15 @@
         <v>-44</v>
       </c>
       <c r="G64" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H64" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I64" t="s">
-        <v>88</v>
-      </c>
-      <c r="X64">
+        <v>98</v>
+      </c>
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3167,7 +3350,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3179,30 +3362,33 @@
         <v>41</v>
       </c>
       <c r="G65" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H65" t="s">
+        <v>43</v>
+      </c>
+      <c r="I65" t="s">
+        <v>44</v>
+      </c>
+      <c r="J65">
+        <v>7</v>
+      </c>
+      <c r="K65" t="s">
         <v>38</v>
       </c>
-      <c r="I65" t="s">
+      <c r="P65" t="s">
         <v>39</v>
       </c>
-      <c r="J65">
-        <v>7</v>
-      </c>
-      <c r="K65" t="s">
-        <v>34</v>
-      </c>
-      <c r="R65" t="s">
-        <v>35</v>
-      </c>
-      <c r="S65" t="s">
-        <v>42</v>
-      </c>
-      <c r="U65" t="s">
-        <v>37</v>
-      </c>
-      <c r="X65">
+      <c r="W65" t="s">
+        <v>40</v>
+      </c>
+      <c r="X65" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB65">
         <v>5</v>
       </c>
     </row>
@@ -3214,7 +3400,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3226,30 +3412,33 @@
         <v>34</v>
       </c>
       <c r="G66" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I66" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>41</v>
-      </c>
-      <c r="R66" t="s">
-        <v>35</v>
-      </c>
-      <c r="S66" t="s">
-        <v>42</v>
-      </c>
-      <c r="U66" t="s">
-        <v>31</v>
-      </c>
-      <c r="X66">
+        <v>47</v>
+      </c>
+      <c r="P66" t="s">
+        <v>39</v>
+      </c>
+      <c r="W66" t="s">
+        <v>40</v>
+      </c>
+      <c r="X66" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3261,7 +3450,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -3273,30 +3462,33 @@
         <v>34</v>
       </c>
       <c r="G67" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I67" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>41</v>
-      </c>
-      <c r="R67" t="s">
-        <v>31</v>
-      </c>
-      <c r="S67" t="s">
-        <v>57</v>
-      </c>
-      <c r="U67" t="s">
-        <v>37</v>
-      </c>
-      <c r="X67">
+        <v>47</v>
+      </c>
+      <c r="P67" t="s">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s">
+        <v>35</v>
+      </c>
+      <c r="X67" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3308,7 +3500,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3320,18 +3512,18 @@
         <v>34</v>
       </c>
       <c r="G68" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>41</v>
-      </c>
-      <c r="X68">
+        <v>47</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3343,7 +3535,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D69">
         <v>4</v>
@@ -3355,18 +3547,18 @@
         <v>34</v>
       </c>
       <c r="G69" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>41</v>
-      </c>
-      <c r="X69">
+        <v>47</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3378,7 +3570,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -3390,27 +3582,30 @@
         <v>34</v>
       </c>
       <c r="G70" t="s">
+        <v>42</v>
+      </c>
+      <c r="H70" t="s">
+        <v>36</v>
+      </c>
+      <c r="I70" t="s">
         <v>37</v>
-      </c>
-      <c r="H70" t="s">
-        <v>32</v>
-      </c>
-      <c r="I70" t="s">
-        <v>33</v>
       </c>
       <c r="J70">
         <v>10</v>
       </c>
-      <c r="R70" t="s">
-        <v>31</v>
-      </c>
-      <c r="S70" t="s">
-        <v>57</v>
-      </c>
-      <c r="U70" t="s">
-        <v>37</v>
-      </c>
-      <c r="X70">
+      <c r="P70" t="s">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s">
+        <v>35</v>
+      </c>
+      <c r="X70" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3422,7 +3617,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3434,30 +3629,33 @@
         <v>24</v>
       </c>
       <c r="G71" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H71" t="s">
+        <v>43</v>
+      </c>
+      <c r="I71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J71">
+        <v>7</v>
+      </c>
+      <c r="K71" t="s">
         <v>38</v>
       </c>
-      <c r="I71" t="s">
+      <c r="P71" t="s">
         <v>39</v>
       </c>
-      <c r="J71">
-        <v>7</v>
-      </c>
-      <c r="K71" t="s">
-        <v>34</v>
-      </c>
-      <c r="R71" t="s">
-        <v>35</v>
-      </c>
-      <c r="S71" t="s">
-        <v>42</v>
-      </c>
-      <c r="U71" t="s">
-        <v>37</v>
-      </c>
-      <c r="X71">
+      <c r="W71" t="s">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3469,7 +3667,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -3481,30 +3679,33 @@
         <v>17</v>
       </c>
       <c r="G72" t="s">
+        <v>42</v>
+      </c>
+      <c r="H72" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" t="s">
         <v>37</v>
-      </c>
-      <c r="H72" t="s">
-        <v>32</v>
-      </c>
-      <c r="I72" t="s">
-        <v>33</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>41</v>
-      </c>
-      <c r="R72" t="s">
-        <v>31</v>
-      </c>
-      <c r="S72" t="s">
-        <v>75</v>
-      </c>
-      <c r="U72" t="s">
-        <v>37</v>
-      </c>
-      <c r="X72">
+        <v>47</v>
+      </c>
+      <c r="P72" t="s">
+        <v>45</v>
+      </c>
+      <c r="W72" t="s">
+        <v>35</v>
+      </c>
+      <c r="X72" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB72">
         <v>5</v>
       </c>
     </row>
@@ -3516,7 +3717,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3528,15 +3729,15 @@
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H73" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="I73" t="s">
-        <v>65</v>
-      </c>
-      <c r="X73">
+        <v>74</v>
+      </c>
+      <c r="AB73">
         <v>5</v>
       </c>
     </row>
@@ -3548,21 +3749,21 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F74">
         <v>-40</v>
       </c>
       <c r="G74" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I74" t="s">
-        <v>47</v>
-      </c>
-      <c r="X74">
+        <v>53</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -3574,7 +3775,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3586,39 +3787,42 @@
         <v>-22</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H75" t="s">
+        <v>43</v>
+      </c>
+      <c r="I75" t="s">
+        <v>44</v>
+      </c>
+      <c r="J75">
+        <v>3</v>
+      </c>
+      <c r="K75" t="s">
         <v>38</v>
-      </c>
-      <c r="I75" t="s">
-        <v>39</v>
-      </c>
-      <c r="J75">
-        <v>3</v>
-      </c>
-      <c r="K75" t="s">
-        <v>34</v>
       </c>
       <c r="L75">
         <v>8</v>
       </c>
       <c r="M75" t="s">
-        <v>49</v>
-      </c>
-      <c r="R75" t="s">
-        <v>31</v>
-      </c>
-      <c r="S75" t="s">
         <v>55</v>
       </c>
-      <c r="T75" t="s">
-        <v>56</v>
-      </c>
-      <c r="U75" t="s">
-        <v>31</v>
-      </c>
-      <c r="X75">
+      <c r="P75" t="s">
+        <v>62</v>
+      </c>
+      <c r="W75" t="s">
+        <v>35</v>
+      </c>
+      <c r="X75" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -3630,7 +3834,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3642,39 +3846,42 @@
         <v>-25</v>
       </c>
       <c r="G76" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H76" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I76" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J76">
         <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L76">
         <v>7</v>
       </c>
       <c r="M76" t="s">
-        <v>59</v>
-      </c>
-      <c r="R76" t="s">
-        <v>37</v>
-      </c>
-      <c r="S76" t="s">
-        <v>55</v>
-      </c>
-      <c r="T76" t="s">
-        <v>90</v>
-      </c>
-      <c r="U76" t="s">
-        <v>37</v>
-      </c>
-      <c r="X76">
+        <v>67</v>
+      </c>
+      <c r="P76" t="s">
+        <v>56</v>
+      </c>
+      <c r="W76" t="s">
+        <v>42</v>
+      </c>
+      <c r="X76" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -3686,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -3698,39 +3905,42 @@
         <v>-30</v>
       </c>
       <c r="G77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H77" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J77">
         <v>5</v>
       </c>
       <c r="K77" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L77">
         <v>8</v>
       </c>
       <c r="M77" t="s">
-        <v>59</v>
-      </c>
-      <c r="R77" t="s">
-        <v>31</v>
-      </c>
-      <c r="S77" t="s">
-        <v>55</v>
-      </c>
-      <c r="T77" t="s">
-        <v>51</v>
-      </c>
-      <c r="U77" t="s">
-        <v>31</v>
-      </c>
-      <c r="X77">
+        <v>67</v>
+      </c>
+      <c r="P77" t="s">
+        <v>56</v>
+      </c>
+      <c r="W77" t="s">
+        <v>35</v>
+      </c>
+      <c r="X77" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -3742,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3754,39 +3964,42 @@
         <v>-35</v>
       </c>
       <c r="G78" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H78" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J78">
         <v>10</v>
       </c>
       <c r="K78" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L78">
         <v>7</v>
       </c>
       <c r="M78" t="s">
-        <v>49</v>
-      </c>
-      <c r="R78" t="s">
-        <v>31</v>
-      </c>
-      <c r="S78" t="s">
-        <v>82</v>
-      </c>
-      <c r="T78" t="s">
-        <v>90</v>
-      </c>
-      <c r="U78" t="s">
-        <v>31</v>
-      </c>
-      <c r="X78">
+        <v>55</v>
+      </c>
+      <c r="P78" t="s">
+        <v>45</v>
+      </c>
+      <c r="W78" t="s">
+        <v>35</v>
+      </c>
+      <c r="X78" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -3798,7 +4011,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3810,42 +4023,45 @@
         <v>-45</v>
       </c>
       <c r="G79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H79" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I79" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J79">
         <v>-2</v>
       </c>
       <c r="K79" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L79">
         <v>7</v>
       </c>
       <c r="M79" t="s">
-        <v>54</v>
-      </c>
-      <c r="R79" t="s">
-        <v>37</v>
-      </c>
-      <c r="S79" t="s">
-        <v>82</v>
-      </c>
-      <c r="T79" t="s">
-        <v>86</v>
-      </c>
-      <c r="U79" t="s">
-        <v>31</v>
-      </c>
-      <c r="V79" t="s">
-        <v>31</v>
-      </c>
-      <c r="X79">
+        <v>61</v>
+      </c>
+      <c r="P79" t="s">
+        <v>45</v>
+      </c>
+      <c r="W79" t="s">
+        <v>42</v>
+      </c>
+      <c r="X79" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -3857,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -3869,19 +4085,19 @@
         <v>-43</v>
       </c>
       <c r="G80" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H80" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I80" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L80">
         <v>6</v>
@@ -3892,19 +4108,22 @@
       <c r="O80">
         <v>1</v>
       </c>
-      <c r="R80" t="s">
-        <v>37</v>
-      </c>
-      <c r="S80" t="s">
-        <v>42</v>
-      </c>
-      <c r="T80" t="s">
-        <v>62</v>
-      </c>
-      <c r="U80" t="s">
-        <v>31</v>
-      </c>
-      <c r="X80">
+      <c r="P80" t="s">
+        <v>45</v>
+      </c>
+      <c r="W80" t="s">
+        <v>42</v>
+      </c>
+      <c r="X80" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB80">
         <v>5</v>
       </c>
     </row>
@@ -3916,7 +4135,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -3928,19 +4147,19 @@
         <v>-43</v>
       </c>
       <c r="G81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H81" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I81" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J81">
         <v>18</v>
       </c>
       <c r="K81" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L81">
         <v>6</v>
@@ -3951,19 +4170,22 @@
       <c r="O81">
         <v>4</v>
       </c>
-      <c r="R81" t="s">
-        <v>37</v>
-      </c>
-      <c r="S81" t="s">
-        <v>57</v>
-      </c>
-      <c r="T81" t="s">
-        <v>91</v>
-      </c>
-      <c r="U81" t="s">
-        <v>37</v>
-      </c>
-      <c r="X81">
+      <c r="P81" t="s">
+        <v>45</v>
+      </c>
+      <c r="W81" t="s">
+        <v>42</v>
+      </c>
+      <c r="X81" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB81">
         <v>5</v>
       </c>
     </row>
@@ -3975,7 +4197,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3987,30 +4209,33 @@
         <v>-39</v>
       </c>
       <c r="G82" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H82" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I82" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J82">
         <v>-5</v>
       </c>
       <c r="K82" t="s">
-        <v>41</v>
-      </c>
-      <c r="R82" t="s">
-        <v>37</v>
-      </c>
-      <c r="S82" t="s">
-        <v>92</v>
-      </c>
-      <c r="U82" t="s">
-        <v>31</v>
-      </c>
-      <c r="X82">
+        <v>47</v>
+      </c>
+      <c r="P82" t="s">
+        <v>45</v>
+      </c>
+      <c r="W82" t="s">
+        <v>42</v>
+      </c>
+      <c r="X82" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB82">
         <v>7</v>
       </c>
     </row>
@@ -4022,7 +4247,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4034,30 +4259,33 @@
         <v>-34</v>
       </c>
       <c r="G83" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H83" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J83">
         <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>34</v>
-      </c>
-      <c r="R83" t="s">
-        <v>37</v>
-      </c>
-      <c r="S83" t="s">
-        <v>92</v>
-      </c>
-      <c r="U83" t="s">
-        <v>37</v>
-      </c>
-      <c r="X83">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>82</v>
+      </c>
+      <c r="W83" t="s">
+        <v>42</v>
+      </c>
+      <c r="X83" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB83">
         <v>7</v>
       </c>
     </row>
@@ -4069,7 +4297,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4081,30 +4309,33 @@
         <v>49</v>
       </c>
       <c r="G84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H84" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I84" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J84">
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>41</v>
-      </c>
-      <c r="R84" t="s">
-        <v>31</v>
-      </c>
-      <c r="S84" t="s">
-        <v>93</v>
-      </c>
-      <c r="U84" t="s">
-        <v>31</v>
-      </c>
-      <c r="X84">
+        <v>47</v>
+      </c>
+      <c r="P84" t="s">
+        <v>45</v>
+      </c>
+      <c r="W84" t="s">
+        <v>35</v>
+      </c>
+      <c r="X84" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB84">
         <v>7</v>
       </c>
     </row>
@@ -4116,7 +4347,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4128,30 +4359,33 @@
         <v>47</v>
       </c>
       <c r="G85" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H85" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I85" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J85">
         <v>5</v>
       </c>
       <c r="K85" t="s">
-        <v>34</v>
-      </c>
-      <c r="R85" t="s">
-        <v>31</v>
-      </c>
-      <c r="S85" t="s">
-        <v>92</v>
-      </c>
-      <c r="U85" t="s">
-        <v>31</v>
-      </c>
-      <c r="X85">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>45</v>
+      </c>
+      <c r="W85" t="s">
+        <v>35</v>
+      </c>
+      <c r="X85" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB85">
         <v>7</v>
       </c>
     </row>
@@ -4163,7 +4397,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -4175,30 +4409,33 @@
         <v>42</v>
       </c>
       <c r="G86" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H86" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>41</v>
-      </c>
-      <c r="R86" t="s">
-        <v>35</v>
-      </c>
-      <c r="S86" t="s">
+        <v>47</v>
+      </c>
+      <c r="P86" t="s">
+        <v>45</v>
+      </c>
+      <c r="W86" t="s">
         <v>40</v>
       </c>
-      <c r="U86" t="s">
-        <v>37</v>
-      </c>
-      <c r="X86">
+      <c r="X86" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB86">
         <v>7</v>
       </c>
     </row>
@@ -4210,7 +4447,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D87">
         <v>4</v>
@@ -4222,24 +4459,27 @@
         <v>42</v>
       </c>
       <c r="G87" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H87" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I87" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J87">
         <v>10</v>
       </c>
       <c r="K87" t="s">
-        <v>34</v>
-      </c>
-      <c r="U87" t="s">
-        <v>31</v>
-      </c>
-      <c r="X87">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB87">
         <v>7</v>
       </c>
     </row>
@@ -4251,7 +4491,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4263,30 +4503,33 @@
         <v>35</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I88" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J88">
         <v>26</v>
       </c>
       <c r="K88" t="s">
-        <v>34</v>
-      </c>
-      <c r="R88" t="s">
-        <v>35</v>
-      </c>
-      <c r="S88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>45</v>
+      </c>
+      <c r="W88" t="s">
         <v>40</v>
       </c>
-      <c r="U88" t="s">
-        <v>37</v>
-      </c>
-      <c r="X88">
+      <c r="X88" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB88">
         <v>7</v>
       </c>
     </row>
@@ -4298,7 +4541,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4310,30 +4553,33 @@
         <v>9</v>
       </c>
       <c r="G89" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H89" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I89" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>41</v>
-      </c>
-      <c r="R89" t="s">
-        <v>31</v>
-      </c>
-      <c r="S89" t="s">
-        <v>57</v>
-      </c>
-      <c r="U89" t="s">
-        <v>37</v>
-      </c>
-      <c r="X89">
+        <v>47</v>
+      </c>
+      <c r="P89" t="s">
+        <v>104</v>
+      </c>
+      <c r="W89" t="s">
+        <v>35</v>
+      </c>
+      <c r="X89" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB89">
         <v>7</v>
       </c>
     </row>
@@ -4345,7 +4591,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4357,33 +4603,36 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H90" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I90" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J90">
         <v>8</v>
       </c>
       <c r="K90" t="s">
-        <v>34</v>
-      </c>
-      <c r="R90" t="s">
-        <v>31</v>
-      </c>
-      <c r="S90" t="s">
-        <v>57</v>
-      </c>
-      <c r="U90" t="s">
-        <v>37</v>
-      </c>
-      <c r="V90" t="s">
-        <v>37</v>
-      </c>
-      <c r="X90">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>30</v>
+      </c>
+      <c r="W90" t="s">
+        <v>35</v>
+      </c>
+      <c r="X90" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB90">
         <v>7</v>
       </c>
     </row>
@@ -4395,7 +4644,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -4407,30 +4656,33 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H91" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I91" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>41</v>
-      </c>
-      <c r="R91" t="s">
-        <v>35</v>
-      </c>
-      <c r="S91" t="s">
+        <v>47</v>
+      </c>
+      <c r="P91" t="s">
+        <v>105</v>
+      </c>
+      <c r="W91" t="s">
         <v>40</v>
       </c>
-      <c r="U91" t="s">
-        <v>37</v>
-      </c>
-      <c r="X91">
+      <c r="X91" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB91">
         <v>7</v>
       </c>
     </row>
@@ -4442,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -4454,30 +4706,33 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H92" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I92" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>41</v>
-      </c>
-      <c r="R92" t="s">
-        <v>35</v>
-      </c>
-      <c r="S92" t="s">
+        <v>47</v>
+      </c>
+      <c r="P92" t="s">
+        <v>45</v>
+      </c>
+      <c r="W92" t="s">
         <v>40</v>
       </c>
-      <c r="U92" t="s">
-        <v>37</v>
-      </c>
-      <c r="X92">
+      <c r="X92" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB92">
         <v>7</v>
       </c>
     </row>
@@ -4489,7 +4744,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D93">
         <v>4</v>
@@ -4501,30 +4756,33 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H93" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J93">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>34</v>
-      </c>
-      <c r="R93" t="s">
-        <v>37</v>
-      </c>
-      <c r="S93" t="s">
-        <v>94</v>
-      </c>
-      <c r="U93" t="s">
-        <v>31</v>
-      </c>
-      <c r="X93">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>45</v>
+      </c>
+      <c r="W93" t="s">
+        <v>42</v>
+      </c>
+      <c r="X93" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB93">
         <v>7</v>
       </c>
     </row>
@@ -4536,21 +4794,21 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F94">
         <v>3</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H94" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I94" t="s">
-        <v>68</v>
-      </c>
-      <c r="X94">
+        <v>77</v>
+      </c>
+      <c r="AB94">
         <v>7</v>
       </c>
     </row>
@@ -4562,7 +4820,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -4571,15 +4829,15 @@
         <v>-25</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H95" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I95" t="s">
-        <v>47</v>
-      </c>
-      <c r="X95">
+        <v>53</v>
+      </c>
+      <c r="AB95">
         <v>8</v>
       </c>
     </row>
@@ -4591,7 +4849,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4603,39 +4861,42 @@
         <v>-37</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H96" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I96" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J96">
         <v>13</v>
       </c>
       <c r="K96" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L96">
         <v>6</v>
       </c>
       <c r="M96" t="s">
-        <v>59</v>
-      </c>
-      <c r="R96" t="s">
-        <v>37</v>
-      </c>
-      <c r="S96" t="s">
-        <v>44</v>
-      </c>
-      <c r="T96" t="s">
-        <v>95</v>
-      </c>
-      <c r="U96" t="s">
-        <v>37</v>
-      </c>
-      <c r="X96">
+        <v>67</v>
+      </c>
+      <c r="P96" t="s">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s">
+        <v>42</v>
+      </c>
+      <c r="X96" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB96">
         <v>6</v>
       </c>
     </row>
@@ -4647,7 +4908,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4659,39 +4920,42 @@
         <v>50</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H97" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I97" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J97">
         <v>6</v>
       </c>
       <c r="K97" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L97">
         <v>6</v>
       </c>
       <c r="M97" t="s">
-        <v>49</v>
-      </c>
-      <c r="R97" t="s">
-        <v>37</v>
-      </c>
-      <c r="S97" t="s">
-        <v>85</v>
-      </c>
-      <c r="T97" t="s">
-        <v>71</v>
-      </c>
-      <c r="U97" t="s">
-        <v>31</v>
-      </c>
-      <c r="X97">
+        <v>55</v>
+      </c>
+      <c r="P97" t="s">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s">
+        <v>42</v>
+      </c>
+      <c r="X97" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB97">
         <v>6</v>
       </c>
     </row>
@@ -4703,7 +4967,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -4715,39 +4979,42 @@
         <v>44</v>
       </c>
       <c r="G98" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H98" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I98" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J98">
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L98">
         <v>7</v>
       </c>
       <c r="M98" t="s">
-        <v>59</v>
-      </c>
-      <c r="R98" t="s">
-        <v>37</v>
-      </c>
-      <c r="S98" t="s">
-        <v>44</v>
-      </c>
-      <c r="T98" t="s">
-        <v>95</v>
-      </c>
-      <c r="U98" t="s">
-        <v>31</v>
-      </c>
-      <c r="X98">
+        <v>67</v>
+      </c>
+      <c r="P98" t="s">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s">
+        <v>42</v>
+      </c>
+      <c r="X98" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB98">
         <v>6</v>
       </c>
     </row>
@@ -4759,7 +5026,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -4771,39 +5038,42 @@
         <v>42</v>
       </c>
       <c r="G99" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H99" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I99" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J99">
         <v>5</v>
       </c>
       <c r="K99" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L99">
         <v>7</v>
       </c>
       <c r="M99" t="s">
-        <v>54</v>
-      </c>
-      <c r="R99" t="s">
-        <v>31</v>
-      </c>
-      <c r="S99" t="s">
-        <v>50</v>
-      </c>
-      <c r="T99" t="s">
-        <v>51</v>
-      </c>
-      <c r="U99" t="s">
-        <v>31</v>
-      </c>
-      <c r="X99">
+        <v>61</v>
+      </c>
+      <c r="P99" t="s">
+        <v>62</v>
+      </c>
+      <c r="W99" t="s">
+        <v>35</v>
+      </c>
+      <c r="X99" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB99">
         <v>6</v>
       </c>
     </row>
@@ -4815,7 +5085,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4827,39 +5097,42 @@
         <v>37</v>
       </c>
       <c r="G100" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H100" t="s">
+        <v>43</v>
+      </c>
+      <c r="I100" t="s">
+        <v>44</v>
+      </c>
+      <c r="J100">
+        <v>3</v>
+      </c>
+      <c r="K100" t="s">
         <v>38</v>
-      </c>
-      <c r="I100" t="s">
-        <v>39</v>
-      </c>
-      <c r="J100">
-        <v>3</v>
-      </c>
-      <c r="K100" t="s">
-        <v>34</v>
       </c>
       <c r="L100">
         <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>49</v>
-      </c>
-      <c r="R100" t="s">
-        <v>37</v>
-      </c>
-      <c r="S100" t="s">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s">
-        <v>90</v>
-      </c>
-      <c r="U100" t="s">
-        <v>37</v>
-      </c>
-      <c r="X100">
+        <v>55</v>
+      </c>
+      <c r="P100" t="s">
+        <v>45</v>
+      </c>
+      <c r="W100" t="s">
+        <v>42</v>
+      </c>
+      <c r="X100" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB100">
         <v>6</v>
       </c>
     </row>
@@ -4871,7 +5144,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -4883,39 +5156,42 @@
         <v>34</v>
       </c>
       <c r="G101" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H101" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I101" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J101">
         <v>34</v>
       </c>
       <c r="K101" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L101">
         <v>7</v>
       </c>
       <c r="M101" t="s">
-        <v>49</v>
-      </c>
-      <c r="R101" t="s">
-        <v>31</v>
-      </c>
-      <c r="S101" t="s">
-        <v>85</v>
-      </c>
-      <c r="T101" t="s">
-        <v>71</v>
-      </c>
-      <c r="U101" t="s">
-        <v>31</v>
-      </c>
-      <c r="X101">
+        <v>55</v>
+      </c>
+      <c r="P101" t="s">
+        <v>30</v>
+      </c>
+      <c r="W101" t="s">
+        <v>35</v>
+      </c>
+      <c r="X101" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB101">
         <v>6</v>
       </c>
     </row>
@@ -4927,7 +5203,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4936,15 +5212,15 @@
         <v>3</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H102" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>65</v>
-      </c>
-      <c r="X102">
+        <v>74</v>
+      </c>
+      <c r="AB102">
         <v>6</v>
       </c>
     </row>
@@ -4956,19 +5232,19 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F103">
         <v>-40</v>
       </c>
       <c r="G103" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H103" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I103" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104">
@@ -4979,7 +5255,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4991,30 +5267,33 @@
         <v>-15</v>
       </c>
       <c r="G104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H104" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I104" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J104">
         <v>-5</v>
       </c>
       <c r="K104" t="s">
-        <v>41</v>
-      </c>
-      <c r="R104" t="s">
-        <v>37</v>
-      </c>
-      <c r="S104" t="s">
-        <v>57</v>
-      </c>
-      <c r="U104" t="s">
-        <v>37</v>
-      </c>
-      <c r="X104">
+        <v>47</v>
+      </c>
+      <c r="P104" t="s">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s">
+        <v>42</v>
+      </c>
+      <c r="X104" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -5026,7 +5305,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5038,30 +5317,33 @@
         <v>-10</v>
       </c>
       <c r="G105" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H105" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I105" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J105">
         <v>13</v>
       </c>
       <c r="K105" t="s">
-        <v>34</v>
-      </c>
-      <c r="R105" t="s">
-        <v>35</v>
-      </c>
-      <c r="S105" t="s">
-        <v>42</v>
-      </c>
-      <c r="U105" t="s">
-        <v>31</v>
-      </c>
-      <c r="X105">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>39</v>
+      </c>
+      <c r="W105" t="s">
+        <v>40</v>
+      </c>
+      <c r="X105" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -5073,7 +5355,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -5085,30 +5367,33 @@
         <v>-23</v>
       </c>
       <c r="G106" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H106" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I106" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J106">
         <v>21</v>
       </c>
       <c r="K106" t="s">
-        <v>34</v>
-      </c>
-      <c r="R106" t="s">
-        <v>35</v>
-      </c>
-      <c r="S106" t="s">
-        <v>42</v>
-      </c>
-      <c r="U106" t="s">
-        <v>37</v>
-      </c>
-      <c r="X106">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>39</v>
+      </c>
+      <c r="W106" t="s">
+        <v>40</v>
+      </c>
+      <c r="X106" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -5120,7 +5405,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -5132,30 +5417,33 @@
         <v>-44</v>
       </c>
       <c r="G107" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H107" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I107" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J107">
         <v>-2</v>
       </c>
       <c r="K107" t="s">
-        <v>41</v>
-      </c>
-      <c r="R107" t="s">
-        <v>31</v>
-      </c>
-      <c r="S107" t="s">
-        <v>57</v>
-      </c>
-      <c r="U107" t="s">
-        <v>31</v>
-      </c>
-      <c r="X107">
+        <v>47</v>
+      </c>
+      <c r="P107" t="s">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s">
+        <v>35</v>
+      </c>
+      <c r="X107" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB107">
         <v>8</v>
       </c>
     </row>
@@ -5167,7 +5455,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -5179,30 +5467,33 @@
         <v>-42</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H108" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I108" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>41</v>
-      </c>
-      <c r="R108" t="s">
-        <v>35</v>
-      </c>
-      <c r="S108" t="s">
-        <v>42</v>
-      </c>
-      <c r="U108" t="s">
-        <v>31</v>
-      </c>
-      <c r="X108">
+        <v>47</v>
+      </c>
+      <c r="P108" t="s">
+        <v>39</v>
+      </c>
+      <c r="W108" t="s">
+        <v>40</v>
+      </c>
+      <c r="X108" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB108">
         <v>8</v>
       </c>
     </row>
@@ -5214,7 +5505,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -5226,30 +5517,33 @@
         <v>-42</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I109" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J109">
         <v>-5</v>
       </c>
       <c r="K109" t="s">
-        <v>41</v>
-      </c>
-      <c r="R109" t="s">
-        <v>35</v>
-      </c>
-      <c r="S109" t="s">
+        <v>47</v>
+      </c>
+      <c r="P109" t="s">
+        <v>39</v>
+      </c>
+      <c r="W109" t="s">
         <v>40</v>
       </c>
-      <c r="U109" t="s">
-        <v>31</v>
-      </c>
-      <c r="X109">
+      <c r="X109" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB109">
         <v>8</v>
       </c>
     </row>
@@ -5261,7 +5555,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -5273,15 +5567,15 @@
         <v>-37</v>
       </c>
       <c r="G110" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H110" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I110" t="s">
-        <v>29</v>
-      </c>
-      <c r="X110">
+        <v>33</v>
+      </c>
+      <c r="AB110">
         <v>8</v>
       </c>
     </row>
@@ -5293,7 +5587,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5305,39 +5599,42 @@
         <v>-30</v>
       </c>
       <c r="G111" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H111" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I111" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J111">
         <v>11</v>
       </c>
       <c r="K111" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L111">
         <v>7</v>
       </c>
       <c r="M111" t="s">
-        <v>49</v>
-      </c>
-      <c r="R111" t="s">
-        <v>31</v>
-      </c>
-      <c r="S111" t="s">
-        <v>85</v>
-      </c>
-      <c r="T111" t="s">
+        <v>55</v>
+      </c>
+      <c r="P111" t="s">
+        <v>82</v>
+      </c>
+      <c r="W111" t="s">
+        <v>35</v>
+      </c>
+      <c r="X111" t="s">
         <v>95</v>
       </c>
-      <c r="U111" t="s">
-        <v>37</v>
-      </c>
-      <c r="X111">
+      <c r="Y111" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB111">
         <v>7</v>
       </c>
     </row>
@@ -5349,7 +5646,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5361,39 +5658,42 @@
         <v>-41</v>
       </c>
       <c r="G112" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H112" t="s">
+        <v>43</v>
+      </c>
+      <c r="I112" t="s">
+        <v>44</v>
+      </c>
+      <c r="J112">
+        <v>3</v>
+      </c>
+      <c r="K112" t="s">
         <v>38</v>
-      </c>
-      <c r="I112" t="s">
-        <v>39</v>
-      </c>
-      <c r="J112">
-        <v>3</v>
-      </c>
-      <c r="K112" t="s">
-        <v>34</v>
       </c>
       <c r="L112">
         <v>8</v>
       </c>
       <c r="M112" t="s">
-        <v>96</v>
-      </c>
-      <c r="R112" t="s">
-        <v>31</v>
-      </c>
-      <c r="S112" t="s">
-        <v>55</v>
-      </c>
-      <c r="T112" t="s">
-        <v>97</v>
-      </c>
-      <c r="U112" t="s">
-        <v>37</v>
-      </c>
-      <c r="X112">
+        <v>108</v>
+      </c>
+      <c r="P112" t="s">
+        <v>109</v>
+      </c>
+      <c r="W112" t="s">
+        <v>35</v>
+      </c>
+      <c r="X112" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB112">
         <v>7</v>
       </c>
     </row>
@@ -5405,7 +5705,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5417,39 +5717,42 @@
         <v>-44</v>
       </c>
       <c r="G113" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H113" t="s">
+        <v>43</v>
+      </c>
+      <c r="I113" t="s">
+        <v>44</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
         <v>38</v>
       </c>
-      <c r="I113" t="s">
-        <v>39</v>
-      </c>
-      <c r="J113">
-        <v>2</v>
-      </c>
-      <c r="K113" t="s">
-        <v>34</v>
-      </c>
       <c r="L113">
         <v>7</v>
       </c>
       <c r="M113" t="s">
-        <v>49</v>
-      </c>
-      <c r="R113" t="s">
-        <v>37</v>
-      </c>
-      <c r="S113" t="s">
-        <v>85</v>
-      </c>
-      <c r="T113" t="s">
-        <v>98</v>
-      </c>
-      <c r="U113" t="s">
-        <v>37</v>
-      </c>
-      <c r="X113">
+        <v>55</v>
+      </c>
+      <c r="P113" t="s">
+        <v>30</v>
+      </c>
+      <c r="W113" t="s">
+        <v>42</v>
+      </c>
+      <c r="X113" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB113">
         <v>7</v>
       </c>
     </row>
@@ -5461,7 +5764,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5473,19 +5776,19 @@
         <v>-46</v>
       </c>
       <c r="G114" t="s">
+        <v>42</v>
+      </c>
+      <c r="H114" t="s">
+        <v>36</v>
+      </c>
+      <c r="I114" t="s">
         <v>37</v>
       </c>
-      <c r="H114" t="s">
-        <v>32</v>
-      </c>
-      <c r="I114" t="s">
-        <v>33</v>
-      </c>
       <c r="J114">
         <v>4</v>
       </c>
       <c r="K114" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L114">
         <v>6</v>
@@ -5496,19 +5799,22 @@
       <c r="O114">
         <v>3</v>
       </c>
-      <c r="R114" t="s">
-        <v>31</v>
-      </c>
-      <c r="S114" t="s">
-        <v>42</v>
-      </c>
-      <c r="T114" t="s">
-        <v>62</v>
-      </c>
-      <c r="U114" t="s">
-        <v>37</v>
-      </c>
-      <c r="X114">
+      <c r="P114" t="s">
+        <v>45</v>
+      </c>
+      <c r="W114" t="s">
+        <v>35</v>
+      </c>
+      <c r="X114" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB114">
         <v>7</v>
       </c>
     </row>
@@ -5520,7 +5826,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -5532,39 +5838,42 @@
         <v>50</v>
       </c>
       <c r="G115" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H115" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I115" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J115">
         <v>3</v>
       </c>
       <c r="K115" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L115">
         <v>7</v>
       </c>
       <c r="M115" t="s">
-        <v>59</v>
-      </c>
-      <c r="R115" t="s">
-        <v>31</v>
-      </c>
-      <c r="S115" t="s">
-        <v>50</v>
-      </c>
-      <c r="T115" t="s">
-        <v>99</v>
-      </c>
-      <c r="U115" t="s">
-        <v>37</v>
-      </c>
-      <c r="X115">
+        <v>67</v>
+      </c>
+      <c r="P115" t="s">
+        <v>112</v>
+      </c>
+      <c r="W115" t="s">
+        <v>35</v>
+      </c>
+      <c r="X115" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB115">
         <v>7</v>
       </c>
     </row>
@@ -5576,7 +5885,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -5588,39 +5897,42 @@
         <v>47</v>
       </c>
       <c r="G116" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H116" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I116" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J116">
         <v>8</v>
       </c>
       <c r="K116" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L116">
         <v>7</v>
       </c>
       <c r="M116" t="s">
-        <v>49</v>
-      </c>
-      <c r="R116" t="s">
-        <v>31</v>
-      </c>
-      <c r="S116" t="s">
-        <v>85</v>
-      </c>
-      <c r="T116" t="s">
+        <v>55</v>
+      </c>
+      <c r="P116" t="s">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s">
+        <v>35</v>
+      </c>
+      <c r="X116" t="s">
         <v>95</v>
       </c>
-      <c r="U116" t="s">
-        <v>31</v>
-      </c>
-      <c r="X116">
+      <c r="Y116" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB116">
         <v>7</v>
       </c>
     </row>
@@ -5632,7 +5944,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -5644,39 +5956,42 @@
         <v>39</v>
       </c>
       <c r="G117" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H117" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I117" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L117">
         <v>7</v>
       </c>
       <c r="M117" t="s">
-        <v>59</v>
-      </c>
-      <c r="R117" t="s">
-        <v>37</v>
-      </c>
-      <c r="S117" t="s">
-        <v>85</v>
-      </c>
-      <c r="T117" t="s">
-        <v>98</v>
-      </c>
-      <c r="U117" t="s">
-        <v>37</v>
-      </c>
-      <c r="X117">
+        <v>67</v>
+      </c>
+      <c r="P117" t="s">
+        <v>30</v>
+      </c>
+      <c r="W117" t="s">
+        <v>42</v>
+      </c>
+      <c r="X117" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB117">
         <v>7</v>
       </c>
     </row>
@@ -5688,7 +6003,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -5700,39 +6015,42 @@
         <v>39</v>
       </c>
       <c r="G118" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H118" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I118" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L118">
         <v>7</v>
       </c>
       <c r="M118" t="s">
-        <v>59</v>
-      </c>
-      <c r="R118" t="s">
-        <v>37</v>
-      </c>
-      <c r="S118" t="s">
-        <v>57</v>
-      </c>
-      <c r="T118" t="s">
-        <v>71</v>
-      </c>
-      <c r="U118" t="s">
-        <v>37</v>
-      </c>
-      <c r="X118">
+        <v>67</v>
+      </c>
+      <c r="P118" t="s">
+        <v>30</v>
+      </c>
+      <c r="W118" t="s">
+        <v>42</v>
+      </c>
+      <c r="X118" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB118">
         <v>7</v>
       </c>
     </row>
@@ -5744,7 +6062,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -5756,39 +6074,42 @@
         <v>39</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H119" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I119" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J119">
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L119">
         <v>8</v>
       </c>
       <c r="M119" t="s">
-        <v>49</v>
-      </c>
-      <c r="R119" t="s">
-        <v>37</v>
-      </c>
-      <c r="S119" t="s">
-        <v>85</v>
-      </c>
-      <c r="T119" t="s">
+        <v>55</v>
+      </c>
+      <c r="P119" t="s">
+        <v>82</v>
+      </c>
+      <c r="W119" t="s">
+        <v>42</v>
+      </c>
+      <c r="X119" t="s">
         <v>95</v>
       </c>
-      <c r="U119" t="s">
-        <v>37</v>
-      </c>
-      <c r="X119">
+      <c r="Y119" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB119">
         <v>7</v>
       </c>
     </row>
@@ -5800,7 +6121,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -5812,19 +6133,19 @@
         <v>37</v>
       </c>
       <c r="G120" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H120" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I120" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J120">
         <v>8</v>
       </c>
       <c r="K120" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L120">
         <v>7</v>
@@ -5835,19 +6156,22 @@
       <c r="O120">
         <v>3</v>
       </c>
-      <c r="R120" t="s">
-        <v>37</v>
-      </c>
-      <c r="S120" t="s">
-        <v>42</v>
-      </c>
-      <c r="T120" t="s">
-        <v>100</v>
-      </c>
-      <c r="U120" t="s">
-        <v>37</v>
-      </c>
-      <c r="X120">
+      <c r="P120" t="s">
+        <v>45</v>
+      </c>
+      <c r="W120" t="s">
+        <v>42</v>
+      </c>
+      <c r="X120" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB120">
         <v>7</v>
       </c>
     </row>
@@ -5859,7 +6183,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -5871,18 +6195,18 @@
         <v>29</v>
       </c>
       <c r="G121" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I121" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>34</v>
-      </c>
-      <c r="X121">
+        <v>38</v>
+      </c>
+      <c r="AB121">
         <v>7</v>
       </c>
     </row>
@@ -5894,7 +6218,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -5906,19 +6230,19 @@
         <v>29</v>
       </c>
       <c r="G122" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I122" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L122">
         <v>7</v>
@@ -5929,19 +6253,22 @@
       <c r="O122">
         <v>5</v>
       </c>
-      <c r="R122" t="s">
-        <v>31</v>
-      </c>
-      <c r="S122" t="s">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s">
-        <v>100</v>
-      </c>
-      <c r="U122" t="s">
-        <v>31</v>
-      </c>
-      <c r="X122">
+      <c r="P122" t="s">
+        <v>45</v>
+      </c>
+      <c r="W122" t="s">
+        <v>35</v>
+      </c>
+      <c r="X122" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB122">
         <v>7</v>
       </c>
     </row>
@@ -5953,7 +6280,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -5965,39 +6292,42 @@
         <v>29</v>
       </c>
       <c r="G123" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H123" t="s">
+        <v>43</v>
+      </c>
+      <c r="I123" t="s">
+        <v>44</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123" t="s">
         <v>38</v>
       </c>
-      <c r="I123" t="s">
-        <v>39</v>
-      </c>
-      <c r="J123">
-        <v>1</v>
-      </c>
-      <c r="K123" t="s">
-        <v>34</v>
-      </c>
       <c r="L123">
         <v>7</v>
       </c>
       <c r="M123" t="s">
-        <v>49</v>
-      </c>
-      <c r="R123" t="s">
-        <v>31</v>
-      </c>
-      <c r="S123" t="s">
-        <v>85</v>
-      </c>
-      <c r="T123" t="s">
-        <v>101</v>
-      </c>
-      <c r="U123" t="s">
-        <v>37</v>
-      </c>
-      <c r="X123">
+        <v>55</v>
+      </c>
+      <c r="P123" t="s">
+        <v>82</v>
+      </c>
+      <c r="W123" t="s">
+        <v>35</v>
+      </c>
+      <c r="X123" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB123">
         <v>7</v>
       </c>
     </row>
@@ -6009,7 +6339,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -6021,39 +6351,42 @@
         <v>28</v>
       </c>
       <c r="G124" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H124" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I124" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J124">
         <v>5</v>
       </c>
       <c r="K124" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L124">
         <v>7</v>
       </c>
       <c r="M124" t="s">
-        <v>49</v>
-      </c>
-      <c r="R124" t="s">
-        <v>37</v>
-      </c>
-      <c r="S124" t="s">
-        <v>85</v>
-      </c>
-      <c r="T124" t="s">
-        <v>60</v>
-      </c>
-      <c r="U124" t="s">
-        <v>37</v>
-      </c>
-      <c r="X124">
+        <v>55</v>
+      </c>
+      <c r="P124" t="s">
+        <v>82</v>
+      </c>
+      <c r="W124" t="s">
+        <v>42</v>
+      </c>
+      <c r="X124" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB124">
         <v>7</v>
       </c>
     </row>
@@ -6065,7 +6398,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -6077,19 +6410,19 @@
         <v>23</v>
       </c>
       <c r="G125" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H125" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I125" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L125">
         <v>6</v>
@@ -6100,19 +6433,22 @@
       <c r="O125">
         <v>9</v>
       </c>
-      <c r="R125" t="s">
-        <v>31</v>
-      </c>
-      <c r="S125" t="s">
-        <v>42</v>
-      </c>
-      <c r="T125" t="s">
-        <v>62</v>
-      </c>
-      <c r="U125" t="s">
-        <v>37</v>
-      </c>
-      <c r="X125">
+      <c r="P125" t="s">
+        <v>45</v>
+      </c>
+      <c r="W125" t="s">
+        <v>35</v>
+      </c>
+      <c r="X125" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB125">
         <v>7</v>
       </c>
     </row>
@@ -6124,7 +6460,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -6136,19 +6472,19 @@
         <v>23</v>
       </c>
       <c r="G126" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I126" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J126">
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L126">
         <v>5</v>
@@ -6159,19 +6495,22 @@
       <c r="O126">
         <v>1</v>
       </c>
-      <c r="R126" t="s">
-        <v>31</v>
-      </c>
-      <c r="S126" t="s">
-        <v>57</v>
-      </c>
-      <c r="T126" t="s">
-        <v>80</v>
-      </c>
-      <c r="U126" t="s">
-        <v>31</v>
-      </c>
-      <c r="X126">
+      <c r="P126" t="s">
+        <v>45</v>
+      </c>
+      <c r="W126" t="s">
+        <v>35</v>
+      </c>
+      <c r="X126" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB126">
         <v>7</v>
       </c>
     </row>
@@ -6183,7 +6522,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D127">
         <v>3</v>
@@ -6195,36 +6534,39 @@
         <v>23</v>
       </c>
       <c r="G127" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H127" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I127" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J127">
         <v>1</v>
       </c>
       <c r="K127" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L127">
         <v>6</v>
       </c>
-      <c r="R127" t="s">
-        <v>31</v>
-      </c>
-      <c r="S127" t="s">
-        <v>57</v>
-      </c>
-      <c r="T127" t="s">
-        <v>91</v>
-      </c>
-      <c r="U127" t="s">
-        <v>37</v>
-      </c>
-      <c r="X127">
+      <c r="P127" t="s">
+        <v>45</v>
+      </c>
+      <c r="W127" t="s">
+        <v>35</v>
+      </c>
+      <c r="X127" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB127">
         <v>7</v>
       </c>
     </row>
@@ -6236,7 +6578,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D128">
         <v>4</v>
@@ -6248,19 +6590,19 @@
         <v>22</v>
       </c>
       <c r="G128" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H128" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I128" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L128">
         <v>5</v>
@@ -6271,19 +6613,22 @@
       <c r="O128">
         <v>9</v>
       </c>
-      <c r="R128" t="s">
-        <v>31</v>
-      </c>
-      <c r="S128" t="s">
-        <v>57</v>
-      </c>
-      <c r="T128" t="s">
-        <v>102</v>
-      </c>
-      <c r="U128" t="s">
-        <v>37</v>
-      </c>
-      <c r="X128">
+      <c r="P128" t="s">
+        <v>45</v>
+      </c>
+      <c r="W128" t="s">
+        <v>35</v>
+      </c>
+      <c r="X128" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB128">
         <v>7</v>
       </c>
     </row>
@@ -6295,7 +6640,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -6307,30 +6652,33 @@
         <v>-22</v>
       </c>
       <c r="G129" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H129" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I129" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J129">
         <v>11</v>
       </c>
       <c r="K129" t="s">
-        <v>34</v>
-      </c>
-      <c r="R129" t="s">
-        <v>35</v>
-      </c>
-      <c r="S129" t="s">
-        <v>36</v>
-      </c>
-      <c r="U129" t="s">
-        <v>37</v>
-      </c>
-      <c r="X129">
+        <v>38</v>
+      </c>
+      <c r="P129" t="s">
+        <v>39</v>
+      </c>
+      <c r="W129" t="s">
+        <v>40</v>
+      </c>
+      <c r="X129" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB129">
         <v>9</v>
       </c>
     </row>
@@ -6342,7 +6690,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -6354,30 +6702,33 @@
         <v>-33</v>
       </c>
       <c r="G130" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H130" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I130" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J130">
         <v>67</v>
       </c>
       <c r="K130" t="s">
-        <v>34</v>
-      </c>
-      <c r="R130" t="s">
-        <v>35</v>
-      </c>
-      <c r="S130" t="s">
-        <v>36</v>
-      </c>
-      <c r="U130" t="s">
-        <v>37</v>
-      </c>
-      <c r="X130">
+        <v>38</v>
+      </c>
+      <c r="P130" t="s">
+        <v>39</v>
+      </c>
+      <c r="W130" t="s">
+        <v>40</v>
+      </c>
+      <c r="X130" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB130">
         <v>9</v>
       </c>
     </row>
@@ -6389,21 +6740,21 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F131">
         <v>3</v>
       </c>
       <c r="G131" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H131" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I131" t="s">
-        <v>65</v>
-      </c>
-      <c r="X131">
+        <v>74</v>
+      </c>
+      <c r="AB131">
         <v>9</v>
       </c>
     </row>
@@ -6415,19 +6766,19 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F132">
         <v>-40</v>
       </c>
       <c r="G132" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H132" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I132" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="133">
@@ -6438,7 +6789,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6450,19 +6801,19 @@
         <v>-30</v>
       </c>
       <c r="G133" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I133" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J133">
         <v>26</v>
       </c>
       <c r="K133" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L133">
         <v>6</v>
@@ -6473,19 +6824,22 @@
       <c r="O133">
         <v>4</v>
       </c>
-      <c r="R133" t="s">
-        <v>37</v>
-      </c>
-      <c r="S133" t="s">
-        <v>57</v>
-      </c>
-      <c r="T133" t="s">
-        <v>62</v>
-      </c>
-      <c r="U133" t="s">
-        <v>31</v>
-      </c>
-      <c r="X133">
+      <c r="P133" t="s">
+        <v>45</v>
+      </c>
+      <c r="W133" t="s">
+        <v>42</v>
+      </c>
+      <c r="X133" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB133">
         <v>8</v>
       </c>
     </row>
@@ -6497,7 +6851,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -6509,36 +6863,39 @@
         <v>44</v>
       </c>
       <c r="G134" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H134" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I134" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J134">
         <v>6</v>
       </c>
       <c r="K134" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L134">
         <v>5</v>
       </c>
-      <c r="R134" t="s">
-        <v>37</v>
-      </c>
-      <c r="S134" t="s">
-        <v>57</v>
-      </c>
-      <c r="T134" t="s">
-        <v>80</v>
-      </c>
-      <c r="U134" t="s">
-        <v>37</v>
-      </c>
-      <c r="X134">
+      <c r="P134" t="s">
+        <v>45</v>
+      </c>
+      <c r="W134" t="s">
+        <v>42</v>
+      </c>
+      <c r="X134" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB134">
         <v>8</v>
       </c>
     </row>
@@ -6550,7 +6907,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -6562,18 +6919,18 @@
         <v>38</v>
       </c>
       <c r="G135" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I135" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>34</v>
-      </c>
-      <c r="X135">
+        <v>38</v>
+      </c>
+      <c r="AB135">
         <v>8</v>
       </c>
     </row>
@@ -6585,7 +6942,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -6597,19 +6954,19 @@
         <v>38</v>
       </c>
       <c r="G136" t="s">
+        <v>42</v>
+      </c>
+      <c r="H136" t="s">
+        <v>36</v>
+      </c>
+      <c r="I136" t="s">
         <v>37</v>
       </c>
-      <c r="H136" t="s">
-        <v>32</v>
-      </c>
-      <c r="I136" t="s">
-        <v>33</v>
-      </c>
       <c r="J136">
         <v>3</v>
       </c>
       <c r="K136" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L136">
         <v>5</v>
@@ -6620,19 +6977,22 @@
       <c r="O136">
         <v>1</v>
       </c>
-      <c r="R136" t="s">
-        <v>31</v>
-      </c>
-      <c r="S136" t="s">
-        <v>57</v>
-      </c>
-      <c r="T136" t="s">
-        <v>80</v>
-      </c>
-      <c r="U136" t="s">
-        <v>31</v>
-      </c>
-      <c r="X136">
+      <c r="P136" t="s">
+        <v>45</v>
+      </c>
+      <c r="W136" t="s">
+        <v>35</v>
+      </c>
+      <c r="X136" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB136">
         <v>8</v>
       </c>
     </row>
@@ -6644,7 +7004,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D137">
         <v>3</v>
@@ -6656,19 +7016,19 @@
         <v>35</v>
       </c>
       <c r="G137" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H137" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I137" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J137">
         <v>5</v>
       </c>
       <c r="K137" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L137">
         <v>6</v>
@@ -6679,16 +7039,19 @@
       <c r="O137">
         <v>3</v>
       </c>
-      <c r="R137" t="s">
-        <v>37</v>
-      </c>
-      <c r="S137" t="s">
-        <v>57</v>
-      </c>
-      <c r="U137" t="s">
-        <v>37</v>
-      </c>
-      <c r="X137">
+      <c r="P137" t="s">
+        <v>45</v>
+      </c>
+      <c r="W137" t="s">
+        <v>42</v>
+      </c>
+      <c r="X137" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB137">
         <v>8</v>
       </c>
     </row>
@@ -6700,7 +7063,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -6712,36 +7075,39 @@
         <v>30</v>
       </c>
       <c r="G138" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H138" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I138" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J138">
         <v>-7</v>
       </c>
       <c r="K138" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L138">
         <v>6</v>
       </c>
-      <c r="R138" t="s">
-        <v>31</v>
-      </c>
-      <c r="S138" t="s">
-        <v>42</v>
-      </c>
-      <c r="T138" t="s">
-        <v>100</v>
-      </c>
-      <c r="U138" t="s">
-        <v>37</v>
-      </c>
-      <c r="X138">
+      <c r="P138" t="s">
+        <v>45</v>
+      </c>
+      <c r="W138" t="s">
+        <v>35</v>
+      </c>
+      <c r="X138" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB138">
         <v>8</v>
       </c>
     </row>
@@ -6753,7 +7119,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -6765,19 +7131,19 @@
         <v>37</v>
       </c>
       <c r="G139" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H139" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I139" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L139">
         <v>6</v>
@@ -6788,19 +7154,22 @@
       <c r="O139">
         <v>8</v>
       </c>
-      <c r="R139" t="s">
-        <v>31</v>
-      </c>
-      <c r="S139" t="s">
-        <v>57</v>
-      </c>
-      <c r="T139" t="s">
-        <v>103</v>
-      </c>
-      <c r="U139" t="s">
-        <v>31</v>
-      </c>
-      <c r="X139">
+      <c r="P139" t="s">
+        <v>45</v>
+      </c>
+      <c r="W139" t="s">
+        <v>35</v>
+      </c>
+      <c r="X139" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB139">
         <v>8</v>
       </c>
     </row>
@@ -6812,7 +7181,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D140">
         <v>3</v>
@@ -6824,19 +7193,19 @@
         <v>37</v>
       </c>
       <c r="G140" t="s">
+        <v>42</v>
+      </c>
+      <c r="H140" t="s">
+        <v>36</v>
+      </c>
+      <c r="I140" t="s">
         <v>37</v>
-      </c>
-      <c r="H140" t="s">
-        <v>32</v>
-      </c>
-      <c r="I140" t="s">
-        <v>33</v>
       </c>
       <c r="J140">
         <v>17</v>
       </c>
       <c r="K140" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L140">
         <v>5</v>
@@ -6847,19 +7216,22 @@
       <c r="O140">
         <v>5</v>
       </c>
-      <c r="R140" t="s">
-        <v>31</v>
-      </c>
-      <c r="S140" t="s">
-        <v>57</v>
-      </c>
-      <c r="T140" t="s">
-        <v>80</v>
-      </c>
-      <c r="U140" t="s">
-        <v>31</v>
-      </c>
-      <c r="X140">
+      <c r="P140" t="s">
+        <v>45</v>
+      </c>
+      <c r="W140" t="s">
+        <v>35</v>
+      </c>
+      <c r="X140" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB140">
         <v>8</v>
       </c>
     </row>
